--- a/templates/Шаблон_спецификации_РД_ИИ.xlsx
+++ b/templates/Шаблон_спецификации_РД_ИИ.xlsx
@@ -11,50 +11,50 @@
     <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Спецификация!$A$2:$I$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Спецификация!$A$2:$J$2</definedName>
     <definedName function="false" hidden="false" name="Классификатор" vbProcedure="false">#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_00A66129_17C8_42A8_8961_8203DB65FC92_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_0285CD8A_BEDF_432A_9372_52E8873AB448_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_06896CFB_F2AB_4557_8DA2_D2641C84E5DC_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_00A66129_17C8_42A8_8961_8203DB65FC92_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_0285CD8A_BEDF_432A_9372_52E8873AB448_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_06896CFB_F2AB_4557_8DA2_D2641C84E5DC_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_195D1089_DFC0_4B4A_8D44_599B43E8B089_.wvu.Cols" vbProcedure="false">спецификация!#REF!,спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_195D1089_DFC0_4B4A_8D44_599B43E8B089_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_195D1089_DFC0_4B4A_8D44_599B43E8B089_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_2CF96EF4_13AA_4F38_BB2D_916B7F773B48_.wvu.Cols" vbProcedure="false">спецификация!#REF!,спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_2CF96EF4_13AA_4F38_BB2D_916B7F773B48_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_3A42A719_6C4A_4ED0_9D8F_E18E3017382A_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_40DA23C6_A0C7_4086_A508_7DC562592190_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_48896570_5E5F_42FF_9E7B_6B7ECC221B0A_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_2CF96EF4_13AA_4F38_BB2D_916B7F773B48_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_3A42A719_6C4A_4ED0_9D8F_E18E3017382A_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_40DA23C6_A0C7_4086_A508_7DC562592190_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_48896570_5E5F_42FF_9E7B_6B7ECC221B0A_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_495FAB80_A14E_4225_ACBC_E8471C36B0B2_.wvu.Cols" vbProcedure="false">спецификация!#REF!,спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_495FAB80_A14E_4225_ACBC_E8471C36B0B2_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_495FAB80_A14E_4225_ACBC_E8471C36B0B2_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_59641797_B514_486E_97EF_91A104456530_.wvu.Cols" vbProcedure="false">спецификация!#REF!,спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_59641797_B514_486E_97EF_91A104456530_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_59641797_B514_486E_97EF_91A104456530_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_5D7D31AB_B764_4570_89CF_22D59A5ACCD4_.wvu.Cols" vbProcedure="false">спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_5D7D31AB_B764_4570_89CF_22D59A5ACCD4_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_5D7D31AB_B764_4570_89CF_22D59A5ACCD4_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_6566A0CE_400F_473B_B381_AB0DA6D973A4_.wvu.Cols" vbProcedure="false">спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_6566A0CE_400F_473B_B381_AB0DA6D973A4_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_6B786D5F_5C15_492A_8646_7423D63CCA12_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_6566A0CE_400F_473B_B381_AB0DA6D973A4_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_6B786D5F_5C15_492A_8646_7423D63CCA12_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_70AD5358_1140_4776_83DB_AE35E4A5B38B_.wvu.Cols" vbProcedure="false">спецификация!#REF!,спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_70AD5358_1140_4776_83DB_AE35E4A5B38B_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_7A5B8DE9_C18F_4926_AC32_CF352943240B_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_7F63FCBA_27E4_4603_9B40_C5145F8F71BD_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_8269109F_FC0C_4DD2_AB0F_46D175C5B48D_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_70AD5358_1140_4776_83DB_AE35E4A5B38B_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_7A5B8DE9_C18F_4926_AC32_CF352943240B_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_7F63FCBA_27E4_4603_9B40_C5145F8F71BD_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_8269109F_FC0C_4DD2_AB0F_46D175C5B48D_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_82EAA34C_B493_4DA2_B2C1_D8A77ED2064E_.wvu.Cols" vbProcedure="false">спецификация!#REF!,спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_82EAA34C_B493_4DA2_B2C1_D8A77ED2064E_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_82EAA34C_B493_4DA2_B2C1_D8A77ED2064E_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_8B8EDE22_910C_49B5_95A4_D4991EE60D22_.wvu.Cols" vbProcedure="false">спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_8B8EDE22_910C_49B5_95A4_D4991EE60D22_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_C9DFB775_9B2B_4C8E_8069_0E24F32CB960_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_8B8EDE22_910C_49B5_95A4_D4991EE60D22_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_C9DFB775_9B2B_4C8E_8069_0E24F32CB960_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_CA850155_8431_40BD_A93D_4A866A13055C_.wvu.Cols" vbProcedure="false">спецификация!#REF!,спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_CA850155_8431_40BD_A93D_4A866A13055C_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_CA850155_8431_40BD_A93D_4A866A13055C_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_CEE10988_0B77_418E_84A0_B6F221101550_.wvu.Cols" vbProcedure="false">спецификация!#REF!,спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_CEE10988_0B77_418E_84A0_B6F221101550_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_CEE10988_0B77_418E_84A0_B6F221101550_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_D6ADC4C1_6A85_44BE_915E_2C427D0A3AED_.wvu.Cols" vbProcedure="false">спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_D6ADC4C1_6A85_44BE_915E_2C427D0A3AED_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_D761632F_8B24_47C1_B1E4_48C8E56C478C_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_D8D6FD87_09B9_4FAA_9FEE_7366CDCC7444_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_D6ADC4C1_6A85_44BE_915E_2C427D0A3AED_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_D761632F_8B24_47C1_B1E4_48C8E56C478C_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_D8D6FD87_09B9_4FAA_9FEE_7366CDCC7444_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_E537F07A_A8E5_41B5_9D99_01037C2F0073_.wvu.Cols" vbProcedure="false">спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_E537F07A_A8E5_41B5_9D99_01037C2F0073_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_F6EABE9C_D87B_4F91_B808_CB4898E4DC4F_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_E537F07A_A8E5_41B5_9D99_01037C2F0073_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_F6EABE9C_D87B_4F91_B808_CB4898E4DC4F_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="Z_FBA94824_8CD6_44E3_A42A_93E26EF07137_.wvu.Cols" vbProcedure="false">спецификация!#REF!,спецификация!#REF!</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="Z_FBA94824_8CD6_44E3_A42A_93E26EF07137_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$H$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="Z_FBA94824_8CD6_44E3_A42A_93E26EF07137_.wvu.FilterData" vbProcedure="false">Спецификация!$A$2:$I$3</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">Поз.</t>
   </si>
@@ -74,10 +74,13 @@
     <t xml:space="preserve">Наименование</t>
   </si>
   <si>
-    <t xml:space="preserve">Модель / ГОСТ / ТУ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Артикул / Код</t>
+    <t xml:space="preserve">ГОСТ / ТУ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Модель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Артикул</t>
   </si>
   <si>
     <t xml:space="preserve">Изготовитель </t>
@@ -219,7 +222,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -249,6 +252,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -546,19 +553,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9.2890625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="5" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="5" width="9.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -574,7 +581,7 @@
       <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="7" t="s">
@@ -592,20 +599,24 @@
       <c r="I2" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="J2" s="7" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="10"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I2"/>
+  <autoFilter ref="A2:J2"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
